--- a/dcf/WIX.xlsx
+++ b/dcf/WIX.xlsx
@@ -164,8 +164,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="172" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="173" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -391,7 +391,7 @@
     </comment>
     <comment ref="B30" authorId="0" shapeId="0">
       <text>
-        <t>Opus: 23.0%</t>
+        <t>User-edited — overridden from Opus 23.0%</t>
       </text>
     </comment>
     <comment ref="B31" authorId="0" shapeId="0">
@@ -1141,25 +1141,25 @@
         <v>9</v>
       </c>
       <c r="B5" s="8" t="n">
-        <v>107.3844030057866</v>
+        <v>72.20335614664864</v>
       </c>
       <c r="C5" s="8" t="n">
-        <v>103.8061179734496</v>
+        <v>70.03842638133072</v>
       </c>
       <c r="D5" s="8" t="n">
-        <v>100.3938123713332</v>
+        <v>67.97346934062359</v>
       </c>
       <c r="E5" s="8" t="n">
-        <v>97.13886146905831</v>
+        <v>66.00329815565561</v>
       </c>
       <c r="F5" s="8" t="n">
-        <v>94.03313135618981</v>
+        <v>64.12302096557575</v>
       </c>
       <c r="G5" s="8" t="n">
-        <v>91.06894873531577</v>
+        <v>62.3280227651911</v>
       </c>
       <c r="H5" s="8" t="n">
-        <v>88.23907270872701</v>
+        <v>60.61394845058433</v>
       </c>
     </row>
     <row r="6">
@@ -1167,25 +1167,25 @@
         <v>10</v>
       </c>
       <c r="B6" s="8" t="n">
-        <v>113.418643463347</v>
+        <v>75.84544836366187</v>
       </c>
       <c r="C6" s="8" t="n">
-        <v>109.5645971738212</v>
+        <v>73.5140771156711</v>
       </c>
       <c r="D6" s="8" t="n">
-        <v>105.8903293793855</v>
+        <v>71.29100730691833</v>
       </c>
       <c r="E6" s="8" t="n">
-        <v>102.3864654955348</v>
+        <v>69.17059947836832</v>
       </c>
       <c r="F6" s="8" t="n">
-        <v>99.04416570146458</v>
+        <v>67.14753570218105</v>
       </c>
       <c r="G6" s="8" t="n">
-        <v>95.85509197230309</v>
+        <v>65.21679976298239</v>
       </c>
       <c r="H6" s="8" t="n">
-        <v>92.81137728995593</v>
+        <v>63.37365864878225</v>
       </c>
     </row>
     <row r="7">
@@ -1193,25 +1193,25 @@
         <v>11</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>119.4528839209073</v>
+        <v>79.4875405806751</v>
       </c>
       <c r="C7" s="8" t="n">
-        <v>115.3230763741929</v>
+        <v>76.98972785001146</v>
       </c>
       <c r="D7" s="8" t="n">
-        <v>111.3868463874379</v>
+        <v>74.60854527321307</v>
       </c>
       <c r="E7" s="8" t="n">
-        <v>107.6340695220113</v>
+        <v>72.33790080108099</v>
       </c>
       <c r="F7" s="8" t="n">
-        <v>104.0552000467393</v>
+        <v>70.17205043878634</v>
       </c>
       <c r="G7" s="8" t="n">
-        <v>100.6412352092904</v>
+        <v>68.10557676077369</v>
       </c>
       <c r="H7" s="8" t="n">
-        <v>97.38368187118485</v>
+        <v>66.13336884698015</v>
       </c>
     </row>
     <row r="8">
@@ -1219,25 +1219,25 @@
         <v>12</v>
       </c>
       <c r="B8" s="8" t="n">
-        <v>125.4871243784677</v>
+        <v>83.12963279768833</v>
       </c>
       <c r="C8" s="8" t="n">
-        <v>121.0815555745645</v>
+        <v>80.46537858435185</v>
       </c>
       <c r="D8" s="8" t="n">
-        <v>116.8833633954902</v>
+        <v>77.9260832395078</v>
       </c>
       <c r="E8" s="54" t="n">
-        <v>112.8816735484878</v>
+        <v>75.50520212379367</v>
       </c>
       <c r="F8" s="8" t="n">
-        <v>109.0662343920141</v>
+        <v>73.19656517539163</v>
       </c>
       <c r="G8" s="8" t="n">
-        <v>105.4273784462777</v>
+        <v>70.99435375856498</v>
       </c>
       <c r="H8" s="8" t="n">
-        <v>101.9559864524138</v>
+        <v>68.89307904517807</v>
       </c>
     </row>
     <row r="9">
@@ -1245,25 +1245,25 @@
         <v>13</v>
       </c>
       <c r="B9" s="8" t="n">
-        <v>131.5213648360281</v>
+        <v>86.77172501470157</v>
       </c>
       <c r="C9" s="8" t="n">
-        <v>126.8400347749361</v>
+        <v>83.94102931869222</v>
       </c>
       <c r="D9" s="8" t="n">
-        <v>122.3798804035426</v>
+        <v>81.24362120580254</v>
       </c>
       <c r="E9" s="8" t="n">
-        <v>118.1292775749643</v>
+        <v>78.67250344650635</v>
       </c>
       <c r="F9" s="8" t="n">
-        <v>114.0772687372889</v>
+        <v>76.22107991199692</v>
       </c>
       <c r="G9" s="8" t="n">
-        <v>110.213521683265</v>
+        <v>73.88313075635627</v>
       </c>
       <c r="H9" s="8" t="n">
-        <v>106.5282910336427</v>
+        <v>71.65278924337598</v>
       </c>
     </row>
     <row r="10">
@@ -1271,25 +1271,25 @@
         <v>14</v>
       </c>
       <c r="B10" s="8" t="n">
-        <v>137.5556052935885</v>
+        <v>90.4138172317148</v>
       </c>
       <c r="C10" s="8" t="n">
-        <v>132.5985139753078</v>
+        <v>87.41668005303259</v>
       </c>
       <c r="D10" s="8" t="n">
-        <v>127.8763974115949</v>
+        <v>84.56115917209728</v>
       </c>
       <c r="E10" s="8" t="n">
-        <v>123.3768816014408</v>
+        <v>81.83980476921904</v>
       </c>
       <c r="F10" s="8" t="n">
-        <v>119.0883030825637</v>
+        <v>79.24559464860222</v>
       </c>
       <c r="G10" s="8" t="n">
-        <v>114.9996649202523</v>
+        <v>76.77190775414758</v>
       </c>
       <c r="H10" s="8" t="n">
-        <v>111.1005956148716</v>
+        <v>74.41249944157389</v>
       </c>
     </row>
     <row r="11">
@@ -1297,25 +1297,25 @@
         <v>15</v>
       </c>
       <c r="B11" s="8" t="n">
-        <v>143.5898457511489</v>
+        <v>94.05590944872803</v>
       </c>
       <c r="C11" s="8" t="n">
-        <v>138.3569931756794</v>
+        <v>90.89233078737297</v>
       </c>
       <c r="D11" s="8" t="n">
-        <v>133.3729144196472</v>
+        <v>87.87869713839201</v>
       </c>
       <c r="E11" s="8" t="n">
-        <v>128.6244856279174</v>
+        <v>85.00710609193173</v>
       </c>
       <c r="F11" s="8" t="n">
-        <v>124.0993374278384</v>
+        <v>82.2701093852075</v>
       </c>
       <c r="G11" s="8" t="n">
-        <v>119.7858081572397</v>
+        <v>79.66068475193886</v>
       </c>
       <c r="H11" s="8" t="n">
-        <v>115.6729001961005</v>
+        <v>77.17220963977179</v>
       </c>
     </row>
     <row r="13">
@@ -1681,7 +1681,7 @@
         </is>
       </c>
       <c r="I8" s="49" t="n">
-        <v>0.8144261599948557</v>
+        <v>0.7695615524109271</v>
       </c>
       <c r="K8" s="25">
         <f>MAX(-0.05,NORMINV(RAND(),$C$6,$D$6))</f>
@@ -24241,7 +24241,7 @@
         </is>
       </c>
       <c r="B30" s="15" t="n">
-        <v>0.23</v>
+        <v>0.19</v>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
@@ -24446,7 +24446,7 @@
         </is>
       </c>
       <c r="B49" s="20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
@@ -24598,13 +24598,13 @@
         </is>
       </c>
       <c r="B58" s="28" t="n">
-        <v>112.8816735484878</v>
+        <v>75.50520212379367</v>
       </c>
       <c r="C58" s="28" t="n">
-        <v>158.8863359047814</v>
+        <v>104.9340803792404</v>
       </c>
       <c r="D58" s="28" t="n">
-        <v>79.60703980101351</v>
+        <v>53.94955326749344</v>
       </c>
     </row>
     <row r="59">
@@ -25007,9 +25007,9 @@
         <f>Dashboard!B30</f>
         <v/>
       </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>Opus</t>
+      <c r="D25" s="32" t="inlineStr">
+        <is>
+          <t>user-edited</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -25017,7 +25017,11 @@
           <t>23.0%</t>
         </is>
       </c>
-      <c r="F25" s="31" t="inlineStr"/>
+      <c r="F25" s="31" t="inlineStr">
+        <is>
+          <t>overridden from Opus 23.0%</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -25138,7 +25142,7 @@
           <t>B40</t>
         </is>
       </c>
-      <c r="C30" s="32">
+      <c r="C30" s="33">
         <f>Dashboard!B40</f>
         <v/>
       </c>
@@ -25250,7 +25254,7 @@
         <f>Dashboard!B45</f>
         <v/>
       </c>
-      <c r="D34" s="33" t="inlineStr">
+      <c r="D34" s="32" t="inlineStr">
         <is>
           <t>user-edited</t>
         </is>
@@ -25281,7 +25285,7 @@
         <f>Dashboard!B46</f>
         <v/>
       </c>
-      <c r="D35" s="33" t="inlineStr">
+      <c r="D35" s="32" t="inlineStr">
         <is>
           <t>user-edited</t>
         </is>
@@ -25811,7 +25815,7 @@
           <t>Beta (levered)</t>
         </is>
       </c>
-      <c r="B4" s="32">
+      <c r="B4" s="33">
         <f>Dashboard!$B$40</f>
         <v/>
       </c>

--- a/dcf/WIX.xlsx
+++ b/dcf/WIX.xlsx
@@ -391,7 +391,7 @@
     </comment>
     <comment ref="B30" authorId="0" shapeId="0">
       <text>
-        <t>User-edited — overridden from Opus 23.0%</t>
+        <t>User-edited — overridden from Opus 23.0% on 2026-07-07</t>
       </text>
     </comment>
     <comment ref="B31" authorId="0" shapeId="0">
@@ -442,12 +442,12 @@
     </comment>
     <comment ref="B45" authorId="0" shapeId="0">
       <text>
-        <t>User-edited — overridden from Opus 15.0x</t>
+        <t>User-edited — overridden from Opus 15.0x on 2026-07-07</t>
       </text>
     </comment>
     <comment ref="B46" authorId="0" shapeId="0">
       <text>
-        <t>User-edited — overridden from Opus 3.5%</t>
+        <t>User-edited — overridden from Opus 3.5% on 2026-07-07</t>
       </text>
     </comment>
     <comment ref="C52" authorId="0" shapeId="0">
@@ -859,7 +859,7 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-08</t>
         </is>
       </c>
     </row>
@@ -25019,7 +25019,7 @@
       </c>
       <c r="F25" s="31" t="inlineStr">
         <is>
-          <t>overridden from Opus 23.0%</t>
+          <t>overridden from Opus 23.0% on 2026-07-07</t>
         </is>
       </c>
     </row>
@@ -25266,7 +25266,7 @@
       </c>
       <c r="F34" s="31" t="inlineStr">
         <is>
-          <t>overridden from Opus 15.0x</t>
+          <t>overridden from Opus 15.0x on 2026-07-07</t>
         </is>
       </c>
     </row>
@@ -25297,7 +25297,7 @@
       </c>
       <c r="F35" s="31" t="inlineStr">
         <is>
-          <t>overridden from Opus 3.5%</t>
+          <t>overridden from Opus 3.5% on 2026-07-07</t>
         </is>
       </c>
     </row>
